--- a/mcp266_conn/mcp266_conn_components.xlsx
+++ b/mcp266_conn/mcp266_conn_components.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arian\Documents\RAMMP\repos\RAMMP-Electronics\mcp266_conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05008BBE-F6FB-43C6-A5AD-B59FD80C23F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C90061-1536-41B8-AF43-4F59A7250940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5BB5F399-4DD8-4676-B938-56FB41703F22}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="headers" sheetId="1" r:id="rId1"/>
+    <sheet name="resistors+caps" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Digikey link</t>
   </si>
@@ -81,15 +82,6 @@
   </si>
   <si>
     <t>CONN HEADER R/A 4POS 2.54MM</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0879110611/3303538</t>
-  </si>
-  <si>
-    <t>WM14829-ND</t>
-  </si>
-  <si>
-    <t>CONN HEADER R/A 6POS 2.54MM</t>
   </si>
 </sst>
 </file>
@@ -494,8 +486,8 @@
     <col min="1" max="1" width="42.109375" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" customWidth="1"/>
     <col min="3" max="4" width="19.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -558,25 +550,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3">
-        <v>879110611</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
@@ -598,8 +578,44 @@
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{FBD183B4-0EE6-4EB6-870E-9EB29FE55C87}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{F650CE11-3E9B-4A93-8938-F962355ED289}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{3B29D7FF-D0A1-43C9-9520-E66EF8EBF1B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A078F289-923B-4000-8275-0691087980EA}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="5" max="5" width="24.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>